--- a/Partes-Interessadas/Partes-Interessadas-modelo.xlsx
+++ b/Partes-Interessadas/Partes-Interessadas-modelo.xlsx
@@ -141,7 +141,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="787" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="787" uniqueCount="397">
   <si>
     <t xml:space="preserve">Partes interessadas — Como usar esta planilha</t>
   </si>
@@ -1031,7 +1031,7 @@
     <t xml:space="preserve">Encerrar as entregas às 22h.</t>
   </si>
   <si>
-    <t xml:space="preserve">O alvará permite funcionar até 23h30, e um terço dos pedidos de sexta e de sábado entra depois das 22h. A loja adotou o requisito do ruído.</t>
+    <t xml:space="preserve">O alvará permite funcionar até a meia-noite, e um terço dos pedidos de sexta e de sábado entra depois das 22h. A loja adotou o requisito do ruído.</t>
   </si>
   <si>
     <t xml:space="preserve">Partes listadas e pertinentes</t>
@@ -1082,7 +1082,7 @@
     <t xml:space="preserve">Aprovam os recursos e definem a estratégia.</t>
   </si>
   <si>
-    <t xml:space="preserve">Análise crítica anual e reunião mensal de resultados.</t>
+    <t xml:space="preserve">Análise crítica a cada semestre e reunião mensal de resultados.</t>
   </si>
   <si>
     <t xml:space="preserve">Coordenador da Qualidade</t>
@@ -1118,13 +1118,13 @@
     <t xml:space="preserve">Renovação da licença e relatórios anuais.</t>
   </si>
   <si>
-    <t xml:space="preserve">Gerente de Produção</t>
+    <t xml:space="preserve">Gerente industrial</t>
   </si>
   <si>
     <t xml:space="preserve">Fornecedores de resina</t>
   </si>
   <si>
-    <t xml:space="preserve">Três itens críticos têm fornecedor único.</t>
+    <t xml:space="preserve">A resina de polietileno tem fornecedor único.</t>
   </si>
   <si>
     <t xml:space="preserve">Previsão trimestral e avaliação a cada semestre.</t>
@@ -1136,10 +1136,10 @@
     <t xml:space="preserve">Organismo de certificação</t>
   </si>
   <si>
-    <t xml:space="preserve">Audita o sistema todo ano e mantém o certificado.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auditoria anual e contato do Coordenador da Qualidade.</t>
+    <t xml:space="preserve">Fará a auditoria de certificação, que dois grandes clientes passaram a exigir.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contratação prevista para 2027 e contato do Coordenador da Qualidade.</t>
   </si>
   <si>
     <t xml:space="preserve">Transportadoras</t>
@@ -1235,16 +1235,22 @@
     <t xml:space="preserve">Abrir o projeto de resina reciclada, com fornecedor homologado.</t>
   </si>
   <si>
-    <t xml:space="preserve">Refugo abaixo de 3% e certificado mantido.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Objetivos da qualidade e ciclo PDCA do refugo.</t>
+    <t xml:space="preserve">Gerente de engenharia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Refugo abaixo de 3% e certificação ISO 9001 obtida.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Refugo de 2,6% em 2026, com o ciclo PDCA. A certificação ainda é um projeto.</t>
   </si>
   <si>
     <t xml:space="preserve">Painel de indicadores, todo mês.</t>
   </si>
   <si>
-    <t xml:space="preserve">Concluir o ciclo PDCA do refugo.</t>
+    <t xml:space="preserve">Contratar a auditoria de certificação.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diretor geral</t>
   </si>
   <si>
     <t xml:space="preserve">Máquinas com proteção e treinamento de segurança em dia.</t>
@@ -1295,7 +1301,7 @@
     <t xml:space="preserve">Avaliação de fornecedores, a cada semestre.</t>
   </si>
   <si>
-    <t xml:space="preserve">Auditoria anual recebida e não conformidades tratadas no prazo.</t>
+    <t xml:space="preserve">Sistema pronto para a auditoria de certificação, com as não conformidades tratadas no prazo.</t>
   </si>
   <si>
     <t xml:space="preserve">Programa de auditorias e controle das não conformidades.</t>
@@ -2212,11 +2218,11 @@
         </c:ser>
         <c:gapWidth val="50"/>
         <c:overlap val="100"/>
-        <c:axId val="33273710"/>
-        <c:axId val="9956136"/>
+        <c:axId val="65762679"/>
+        <c:axId val="12736261"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="33273710"/>
+        <c:axId val="65762679"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -2248,7 +2254,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="9956136"/>
+        <c:crossAx val="12736261"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2256,7 +2262,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="9956136"/>
+        <c:axId val="12736261"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -2296,7 +2302,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="33273710"/>
+        <c:crossAx val="65762679"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
@@ -4662,10 +4668,6 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="5">
-    <dataValidation allowBlank="true" error="Digite uma data no formato dia/mês/ano." errorStyle="stop" errorTitle="Data inválida" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L7:L46" type="date">
-      <formula1>36526</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
     <dataValidation allowBlank="true" error="Escolha uma parte cadastrada na aba Partes." errorStyle="stop" errorTitle="Parte inválida" operator="between" prompt="Escolha uma parte da lista da aba Partes." promptTitle="Parte" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="C7:C46" type="list">
       <formula1>Partes!$C$11:$C$22</formula1>
       <formula2>0</formula2>
@@ -4680,6 +4682,10 @@
     </dataValidation>
     <dataValidation allowBlank="true" error="Escolha uma das opções da lista." errorStyle="stop" errorTitle="Valor inválido" operator="between" prompt="Situação do requisito adotado" promptTitle="Opções" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="I7:I46" type="list">
       <formula1>"Atende,Atende em parte,Não atende"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Digite uma data no formato dia/mês/ano." errorStyle="stop" errorTitle="Data inválida" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L7:L46" type="date">
+      <formula1>36526</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -8128,7 +8134,7 @@
         <v>Sim</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="12" t="n">
         <v>8</v>
       </c>
@@ -8567,7 +8573,7 @@
         <v>363</v>
       </c>
       <c r="K32" s="7" t="s">
-        <v>325</v>
+        <v>364</v>
       </c>
       <c r="L32" s="42" t="n">
         <v>46568</v>
@@ -8581,7 +8587,7 @@
         <v>311</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E33" s="40" t="s">
         <v>253</v>
@@ -8590,19 +8596,19 @@
         <v>91</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="I33" s="40" t="s">
         <v>122</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K33" s="7" t="s">
-        <v>325</v>
+        <v>369</v>
       </c>
       <c r="L33" s="42" t="n">
         <v>46507</v>
@@ -8616,7 +8622,7 @@
         <v>315</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="E34" s="40" t="s">
         <v>119</v>
@@ -8625,10 +8631,10 @@
         <v>91</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="H34" s="7" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="I34" s="40" t="s">
         <v>172</v>
@@ -8651,7 +8657,7 @@
         <v>315</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E35" s="40" t="s">
         <v>253</v>
@@ -8660,16 +8666,16 @@
         <v>91</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="I35" s="40" t="s">
         <v>122</v>
       </c>
       <c r="J35" s="7" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="K35" s="7" t="s">
         <v>318</v>
@@ -8686,7 +8692,7 @@
         <v>319</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E36" s="40" t="s">
         <v>119</v>
@@ -8695,10 +8701,10 @@
         <v>91</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="H36" s="7" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="I36" s="40" t="s">
         <v>172</v>
@@ -8721,7 +8727,7 @@
         <v>322</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="E37" s="40" t="s">
         <v>119</v>
@@ -8730,10 +8736,10 @@
         <v>91</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="H37" s="7" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="I37" s="40" t="s">
         <v>172</v>
@@ -8756,7 +8762,7 @@
         <v>326</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="E38" s="40" t="s">
         <v>249</v>
@@ -8765,10 +8771,10 @@
         <v>91</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="H38" s="7" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I38" s="40" t="s">
         <v>172</v>
@@ -8783,7 +8789,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="12" t="n">
         <v>13</v>
       </c>
@@ -8791,19 +8797,19 @@
         <v>330</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="E39" s="40" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="F39" s="40" t="s">
         <v>91</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="I39" s="40" t="s">
         <v>172</v>
@@ -8826,7 +8832,7 @@
         <v>333</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="E40" s="40" t="s">
         <v>249</v>
@@ -8835,10 +8841,10 @@
         <v>91</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="H40" s="7" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="I40" s="40" t="s">
         <v>172</v>
@@ -8861,7 +8867,7 @@
         <v>336</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E41" s="40" t="s">
         <v>253</v>
@@ -8870,10 +8876,10 @@
         <v>91</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="H41" s="7" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="I41" s="40" t="s">
         <v>172</v>
@@ -8896,7 +8902,7 @@
         <v>336</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="E42" s="40" t="s">
         <v>253</v>
@@ -8905,7 +8911,7 @@
         <v>214</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="H42" s="7" t="s">
         <v>244</v>

--- a/Partes-Interessadas/Partes-Interessadas-modelo.xlsx
+++ b/Partes-Interessadas/Partes-Interessadas-modelo.xlsx
@@ -992,7 +992,7 @@
     <t xml:space="preserve">Cumprir as boas práticas de manipulação: temperatura, higiene e controle de pragas.</t>
   </si>
   <si>
-    <t xml:space="preserve">Manual de boas práticas e registro de temperatura, duas vezes por turno.</t>
+    <t xml:space="preserve">Manual de boas práticas e registro de temperatura, uma vez em cada turno.</t>
   </si>
   <si>
     <t xml:space="preserve">Registros de temperatura, conferidos toda semana.</t>
@@ -2218,11 +2218,11 @@
         </c:ser>
         <c:gapWidth val="50"/>
         <c:overlap val="100"/>
-        <c:axId val="65762679"/>
-        <c:axId val="12736261"/>
+        <c:axId val="95986590"/>
+        <c:axId val="20939031"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="65762679"/>
+        <c:axId val="95986590"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -2254,7 +2254,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="12736261"/>
+        <c:crossAx val="20939031"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2262,7 +2262,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="12736261"/>
+        <c:axId val="20939031"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -2302,7 +2302,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="65762679"/>
+        <c:crossAx val="95986590"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
@@ -4668,6 +4668,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="5">
+    <dataValidation allowBlank="true" error="Digite uma data no formato dia/mês/ano." errorStyle="stop" errorTitle="Data inválida" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L7:L46" type="date">
+      <formula1>36526</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
     <dataValidation allowBlank="true" error="Escolha uma parte cadastrada na aba Partes." errorStyle="stop" errorTitle="Parte inválida" operator="between" prompt="Escolha uma parte da lista da aba Partes." promptTitle="Parte" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="C7:C46" type="list">
       <formula1>Partes!$C$11:$C$22</formula1>
       <formula2>0</formula2>
@@ -4682,10 +4686,6 @@
     </dataValidation>
     <dataValidation allowBlank="true" error="Escolha uma das opções da lista." errorStyle="stop" errorTitle="Valor inválido" operator="between" prompt="Situação do requisito adotado" promptTitle="Opções" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="I7:I46" type="list">
       <formula1>"Atende,Atende em parte,Não atende"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Digite uma data no formato dia/mês/ano." errorStyle="stop" errorTitle="Data inválida" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L7:L46" type="date">
-      <formula1>36526</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
